--- a/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_46.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_46.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3187669.416017215</v>
+        <v>3180692.031325087</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9956801.353979917</v>
+        <v>9956801.353979921</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9956801.353979917</v>
+        <v>9956801.353979921</v>
       </c>
     </row>
     <row r="9">
@@ -657,7 +657,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>49.47457824299391</v>
+        <v>217.8895696284084</v>
       </c>
       <c r="D2" t="n">
         <v>10.33915573984979</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>168.4149913854146</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>94.84816780232291</v>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>241.3273244538894</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -778,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>421</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S3" t="n">
         <v>66.5639999646113</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>300.0898026466166</v>
       </c>
     </row>
     <row r="4">
@@ -906,7 +906,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>172.1723636724307</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
         <v>8.009658703527407</v>
@@ -948,7 +948,7 @@
         <v>186.6755817285639</v>
       </c>
       <c r="U5" t="n">
-        <v>249.2212965486107</v>
+        <v>417.6362879340252</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -973,13 +973,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>240.5992384920742</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>107.9988548477319</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1027,13 +1027,13 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2103597601867477</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>421</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1182,7 +1182,7 @@
         <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
-        <v>186.6755817285639</v>
+        <v>355.0905731139785</v>
       </c>
       <c r="U8" t="n">
         <v>249.2212965486107</v>
@@ -1191,7 +1191,7 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>406.7884673663621</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X8" t="n">
         <v>192.2818334606677</v>
@@ -1213,13 +1213,13 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>119.582286503892</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,19 +1252,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>184.6533820101571</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
         <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>400.2103597601867</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1386,7 +1386,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1428,7 +1428,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>288.3734759809475</v>
+        <v>292.3388673663621</v>
       </c>
       <c r="X11" t="n">
         <v>242.2818334606677</v>
@@ -1450,13 +1450,13 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>86.93822665041522</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>325.7395358750273</v>
@@ -1623,7 +1623,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T14" t="n">
         <v>236.6755817285639</v>
@@ -1690,10 +1690,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>73.04152018756569</v>
       </c>
       <c r="F15" t="n">
-        <v>62.67776252544243</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S15" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T15" t="n">
         <v>55.35776521751382</v>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>135.964704340989</v>
+        <v>131.9993129555745</v>
       </c>
       <c r="C17" t="n">
         <v>99.47457824299391</v>
@@ -1860,7 +1860,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>80.50967533902144</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>73.0415201875656</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>197.2737972923793</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T20" t="n">
         <v>236.6755817285639</v>
@@ -2139,7 +2139,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>288.3734759809475</v>
+        <v>292.3388673663621</v>
       </c>
       <c r="X20" t="n">
         <v>242.2818334606677</v>
@@ -2215,16 +2215,16 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V21" t="n">
-        <v>127.1884297169627</v>
+        <v>127.1884297169626</v>
       </c>
       <c r="W21" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
         <v>69.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="22">
@@ -2361,13 +2361,13 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S23" t="n">
         <v>144.8481678023229</v>
       </c>
       <c r="T23" t="n">
-        <v>240.6409731139784</v>
+        <v>236.6755817285639</v>
       </c>
       <c r="U23" t="n">
         <v>299.2212965486107</v>
@@ -2395,19 +2395,19 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>70.00566530352997</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>62.67776252544254</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2601,13 +2601,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T26" t="n">
         <v>236.6755817285639</v>
       </c>
       <c r="U26" t="n">
-        <v>303.1866879340253</v>
+        <v>299.2212965486107</v>
       </c>
       <c r="V26" t="n">
         <v>279.8510241668239</v>
@@ -2635,7 +2635,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V27" t="n">
-        <v>145.0203425305416</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W27" t="n">
         <v>82.37314290982852</v>
@@ -2698,7 +2698,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>49.39139276613435</v>
+        <v>114.1314683938743</v>
       </c>
     </row>
     <row r="28">
@@ -2844,7 +2844,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>299.2212965486107</v>
+        <v>303.1866879340253</v>
       </c>
       <c r="V29" t="n">
         <v>279.8510241668239</v>
@@ -2853,7 +2853,7 @@
         <v>288.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>246.2472248460823</v>
+        <v>242.2818334606677</v>
       </c>
       <c r="Y29" t="n">
         <v>161.3174326828064</v>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C30" t="n">
         <v>11.09991244551929</v>
@@ -2884,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S30" t="n">
-        <v>179.2417624900538</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T30" t="n">
         <v>55.35776521751382</v>
@@ -2929,7 +2929,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W30" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X30" t="n">
         <v>69.86273944538755</v>
@@ -3036,7 +3036,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F32" t="n">
-        <v>54.88962870801186</v>
+        <v>58.85502009342638</v>
       </c>
       <c r="G32" t="n">
         <v>53.75737228701621</v>
@@ -3045,7 +3045,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I32" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3160,19 +3160,19 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U33" t="n">
-        <v>112.8881222856293</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V33" t="n">
         <v>64.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
         <v>69.86273944538755</v>
       </c>
       <c r="Y33" t="n">
-        <v>399.3913927661343</v>
+        <v>112.0691552915768</v>
       </c>
     </row>
     <row r="34">
@@ -3276,13 +3276,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H35" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3343,19 +3343,19 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>81.10557774904923</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>86.93822665041522</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
         <v>60.33915573984979</v>
       </c>
       <c r="E38" t="n">
-        <v>58.32868099228319</v>
+        <v>54.36328960686865</v>
       </c>
       <c r="F38" t="n">
         <v>54.88962870801186</v>
@@ -3519,7 +3519,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>86.93822665041522</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3592,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S39" t="n">
         <v>116.5639999646113</v>
@@ -3637,7 +3637,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V39" t="n">
-        <v>64.51066719152016</v>
+        <v>127.1884297169626</v>
       </c>
       <c r="W39" t="n">
         <v>82.37314290982852</v>
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S41" t="n">
         <v>144.8481678023229</v>
@@ -3820,7 +3820,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -3859,13 +3859,13 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>62.67776252544251</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>197.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T42" t="n">
         <v>55.35776521751382</v>
@@ -3874,7 +3874,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V42" t="n">
-        <v>64.51066719152016</v>
+        <v>129.2507428192602</v>
       </c>
       <c r="W42" t="n">
         <v>82.37314290982852</v>
@@ -3984,7 +3984,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F44" t="n">
-        <v>54.88962870801186</v>
+        <v>58.85502009342638</v>
       </c>
       <c r="G44" t="n">
         <v>53.75737228701621</v>
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>11.09991244551929</v>
@@ -4102,7 +4102,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>55.35776521751382</v>
@@ -4114,13 +4114,13 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>145.0509054352709</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X45" t="n">
         <v>69.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>49.39139276613435</v>
+        <v>112.0691552915768</v>
       </c>
     </row>
     <row r="46">
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>115.3301851396645</v>
+        <v>285.4463380542246</v>
       </c>
       <c r="C2" t="n">
         <v>65.35586368209485</v>
@@ -4321,19 +4321,19 @@
         <v>33.68</v>
       </c>
       <c r="J2" t="n">
-        <v>424.9891130376557</v>
+        <v>33.68</v>
       </c>
       <c r="K2" t="n">
-        <v>424.9891130376557</v>
+        <v>433.6300000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>424.9891130376557</v>
+        <v>433.6300000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>841.7791130376559</v>
+        <v>850.4200000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>1258.569113037656</v>
+        <v>1267.21</v>
       </c>
       <c r="O2" t="n">
         <v>1267.21</v>
@@ -4345,28 +4345,28 @@
         <v>1684</v>
       </c>
       <c r="R2" t="n">
-        <v>1513.88384708544</v>
+        <v>1684</v>
       </c>
       <c r="S2" t="n">
-        <v>1418.077616982083</v>
+        <v>1588.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>1229.516423316867</v>
+        <v>1399.632576231427</v>
       </c>
       <c r="U2" t="n">
-        <v>977.7777399344324</v>
+        <v>1147.893892848992</v>
       </c>
       <c r="V2" t="n">
-        <v>745.6049882507718</v>
+        <v>915.7211411653319</v>
       </c>
       <c r="W2" t="n">
-        <v>504.8236993811278</v>
+        <v>674.9398522956878</v>
       </c>
       <c r="X2" t="n">
-        <v>310.5996251784331</v>
+        <v>480.7157780929932</v>
       </c>
       <c r="Y2" t="n">
-        <v>198.1577739836791</v>
+        <v>368.2739268982392</v>
       </c>
     </row>
     <row r="3">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>623.5784057331334</v>
+        <v>33.68</v>
       </c>
       <c r="C3" t="n">
-        <v>623.5784057331334</v>
+        <v>33.68</v>
       </c>
       <c r="D3" t="n">
-        <v>623.5784057331334</v>
+        <v>33.68</v>
       </c>
       <c r="E3" t="n">
-        <v>277.4449741958479</v>
+        <v>33.68</v>
       </c>
       <c r="F3" t="n">
-        <v>277.4449741958479</v>
+        <v>33.68</v>
       </c>
       <c r="G3" t="n">
-        <v>277.4449741958479</v>
+        <v>33.68</v>
       </c>
       <c r="H3" t="n">
         <v>33.68</v>
@@ -4421,31 +4421,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1189.112420368536</v>
+        <v>1014.284879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>763.8598951160103</v>
+        <v>865.523468466658</v>
       </c>
       <c r="S3" t="n">
-        <v>696.6235315153929</v>
+        <v>798.2871048660405</v>
       </c>
       <c r="T3" t="n">
-        <v>691.2116474572981</v>
+        <v>792.8752208079458</v>
       </c>
       <c r="U3" t="n">
-        <v>690.9991628510488</v>
+        <v>792.6627362016965</v>
       </c>
       <c r="V3" t="n">
-        <v>676.3419232636547</v>
+        <v>778.0054966143024</v>
       </c>
       <c r="W3" t="n">
-        <v>643.6417789102926</v>
+        <v>745.3053522609403</v>
       </c>
       <c r="X3" t="n">
-        <v>623.5784057331334</v>
+        <v>725.2419790837811</v>
       </c>
       <c r="Y3" t="n">
-        <v>623.5784057331334</v>
+        <v>422.1209663094209</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>327.3530308546201</v>
+        <v>445.127684463691</v>
       </c>
       <c r="C4" t="n">
-        <v>453.3550366730559</v>
+        <v>528.9830385051386</v>
       </c>
       <c r="D4" t="n">
-        <v>566.674180798056</v>
+        <v>528.9830385051386</v>
       </c>
       <c r="E4" t="n">
-        <v>684.503085009469</v>
+        <v>528.9830385051386</v>
       </c>
       <c r="F4" t="n">
-        <v>808.8640576014045</v>
+        <v>528.9830385051386</v>
       </c>
       <c r="G4" t="n">
-        <v>962.2706234882897</v>
+        <v>682.3896043920238</v>
       </c>
       <c r="H4" t="n">
-        <v>962.2706234882897</v>
+        <v>851.9061895514213</v>
       </c>
       <c r="I4" t="n">
-        <v>1183.403502424373</v>
+        <v>1073.039068487504</v>
       </c>
       <c r="J4" t="n">
-        <v>1544.487243076824</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="K4" t="n">
         <v>1544.487243076824</v>
@@ -4506,25 +4506,25 @@
         <v>33.68</v>
       </c>
       <c r="S4" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>221.7556791588049</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="U4" t="n">
-        <v>221.7556791588049</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="V4" t="n">
-        <v>221.7556791588049</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="W4" t="n">
-        <v>221.7556791588049</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="X4" t="n">
-        <v>221.7556791588049</v>
+        <v>221.9610461183667</v>
       </c>
       <c r="Y4" t="n">
-        <v>327.3530308546201</v>
+        <v>333.3703467973989</v>
       </c>
     </row>
     <row r="5">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>285.4463380542246</v>
+        <v>115.3301851396645</v>
       </c>
       <c r="C5" t="n">
-        <v>235.472016596655</v>
+        <v>65.35586368209485</v>
       </c>
       <c r="D5" t="n">
-        <v>225.028424940241</v>
+        <v>54.91227202568093</v>
       </c>
       <c r="E5" t="n">
-        <v>220.6210617009798</v>
+        <v>50.50490878641967</v>
       </c>
       <c r="F5" t="n">
-        <v>215.6820428039981</v>
+        <v>45.565889889438</v>
       </c>
       <c r="G5" t="n">
         <v>41.77056434699738</v>
@@ -4558,19 +4558,19 @@
         <v>33.68</v>
       </c>
       <c r="J5" t="n">
-        <v>33.68</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="K5" t="n">
-        <v>450.47</v>
+        <v>841.7791130376557</v>
       </c>
       <c r="L5" t="n">
-        <v>867.26</v>
+        <v>1258.569113037656</v>
       </c>
       <c r="M5" t="n">
-        <v>1267.21</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="N5" t="n">
-        <v>1267.21</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="O5" t="n">
         <v>1684</v>
@@ -4591,19 +4591,19 @@
         <v>1399.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>1147.893892848992</v>
+        <v>977.7777399344324</v>
       </c>
       <c r="V5" t="n">
-        <v>915.7211411653319</v>
+        <v>745.6049882507718</v>
       </c>
       <c r="W5" t="n">
-        <v>674.9398522956878</v>
+        <v>504.8236993811278</v>
       </c>
       <c r="X5" t="n">
-        <v>480.7157780929932</v>
+        <v>310.5996251784331</v>
       </c>
       <c r="Y5" t="n">
-        <v>368.2739268982392</v>
+        <v>198.1577739836791</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>507.5171386800518</v>
+        <v>496.0291155388109</v>
       </c>
       <c r="C6" t="n">
-        <v>142.7697523714464</v>
+        <v>496.0291155388109</v>
       </c>
       <c r="D6" t="n">
-        <v>142.7697523714464</v>
+        <v>496.0291155388109</v>
       </c>
       <c r="E6" t="n">
-        <v>142.7697523714464</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="F6" t="n">
-        <v>142.7697523714464</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="G6" t="n">
-        <v>142.7697523714464</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="H6" t="n">
-        <v>142.7697523714464</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="I6" t="n">
         <v>33.68</v>
@@ -4670,19 +4670,19 @@
         <v>967.7027613033796</v>
       </c>
       <c r="U6" t="n">
-        <v>967.4902766971303</v>
+        <v>563.4498726567263</v>
       </c>
       <c r="V6" t="n">
-        <v>952.8330371097362</v>
+        <v>548.7926330693322</v>
       </c>
       <c r="W6" t="n">
-        <v>527.5805118572109</v>
+        <v>516.09248871597</v>
       </c>
       <c r="X6" t="n">
-        <v>507.5171386800518</v>
+        <v>496.0291155388109</v>
       </c>
       <c r="Y6" t="n">
-        <v>507.5171386800518</v>
+        <v>496.0291155388109</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1213.216612312233</v>
+        <v>1025.140933153428</v>
       </c>
       <c r="C7" t="n">
-        <v>1213.216612312233</v>
+        <v>1151.142938971864</v>
       </c>
       <c r="D7" t="n">
-        <v>1213.216612312233</v>
+        <v>1264.462083096864</v>
       </c>
       <c r="E7" t="n">
-        <v>1213.216612312233</v>
+        <v>1382.290987308277</v>
       </c>
       <c r="F7" t="n">
-        <v>1213.216612312233</v>
+        <v>1506.651959900212</v>
       </c>
       <c r="G7" t="n">
-        <v>1213.216612312233</v>
+        <v>1506.651959900212</v>
       </c>
       <c r="H7" t="n">
-        <v>1382.733197471631</v>
+        <v>1506.651959900212</v>
       </c>
       <c r="I7" t="n">
-        <v>1434.122809139956</v>
+        <v>1506.651959900212</v>
       </c>
       <c r="J7" t="n">
-        <v>1434.122809139956</v>
+        <v>1506.651959900212</v>
       </c>
       <c r="K7" t="n">
         <v>1544.487243076824</v>
@@ -4746,22 +4746,22 @@
         <v>33.68</v>
       </c>
       <c r="T7" t="n">
-        <v>221.7556791588049</v>
+        <v>33.68</v>
       </c>
       <c r="U7" t="n">
-        <v>468.3068717970915</v>
+        <v>280.2311926382866</v>
       </c>
       <c r="V7" t="n">
-        <v>667.1282646830375</v>
+        <v>479.0525855242326</v>
       </c>
       <c r="W7" t="n">
-        <v>839.0191829427149</v>
+        <v>650.94350378391</v>
       </c>
       <c r="X7" t="n">
-        <v>990.0499739669084</v>
+        <v>801.9742948081035</v>
       </c>
       <c r="Y7" t="n">
-        <v>1101.459274645941</v>
+        <v>913.3835954871358</v>
       </c>
     </row>
     <row r="8">
@@ -4795,22 +4795,22 @@
         <v>33.68</v>
       </c>
       <c r="J8" t="n">
-        <v>33.68</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="K8" t="n">
-        <v>33.68</v>
+        <v>841.7791130376557</v>
       </c>
       <c r="L8" t="n">
-        <v>33.68</v>
+        <v>1258.569113037656</v>
       </c>
       <c r="M8" t="n">
-        <v>450.47</v>
+        <v>1267.21</v>
       </c>
       <c r="N8" t="n">
-        <v>867.26</v>
+        <v>1684</v>
       </c>
       <c r="O8" t="n">
-        <v>1267.21</v>
+        <v>1684</v>
       </c>
       <c r="P8" t="n">
         <v>1684</v>
@@ -4825,13 +4825,13 @@
         <v>1588.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>1399.632576231427</v>
+        <v>1229.516423316867</v>
       </c>
       <c r="U8" t="n">
-        <v>1147.893892848992</v>
+        <v>977.7777399344324</v>
       </c>
       <c r="V8" t="n">
-        <v>915.7211411653319</v>
+        <v>745.6049882507718</v>
       </c>
       <c r="W8" t="n">
         <v>504.8236993811278</v>
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>376.7469114524009</v>
+        <v>725.2419790837811</v>
       </c>
       <c r="C9" t="n">
-        <v>376.7469114524009</v>
+        <v>725.2419790837811</v>
       </c>
       <c r="D9" t="n">
-        <v>376.7469114524009</v>
+        <v>373.7897700962026</v>
       </c>
       <c r="E9" t="n">
-        <v>376.7469114524009</v>
+        <v>373.7897700962026</v>
       </c>
       <c r="F9" t="n">
-        <v>33.68</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="G9" t="n">
-        <v>33.68</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="H9" t="n">
-        <v>33.68</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="I9" t="n">
         <v>33.68</v>
@@ -4895,31 +4895,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1189.112420368536</v>
+        <v>1014.284879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>1040.351008962092</v>
+        <v>865.523468466658</v>
       </c>
       <c r="S9" t="n">
-        <v>853.8324412750644</v>
+        <v>798.2871048660405</v>
       </c>
       <c r="T9" t="n">
-        <v>848.4205572169697</v>
+        <v>792.8752208079458</v>
       </c>
       <c r="U9" t="n">
-        <v>444.1676685703163</v>
+        <v>792.6627362016965</v>
       </c>
       <c r="V9" t="n">
-        <v>429.5104289829222</v>
+        <v>778.0054966143024</v>
       </c>
       <c r="W9" t="n">
-        <v>396.81028462956</v>
+        <v>745.3053522609403</v>
       </c>
       <c r="X9" t="n">
-        <v>376.7469114524009</v>
+        <v>725.2419790837811</v>
       </c>
       <c r="Y9" t="n">
-        <v>376.7469114524009</v>
+        <v>725.2419790837811</v>
       </c>
     </row>
     <row r="10">
@@ -4929,16 +4929,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>402.9810326867027</v>
+        <v>242.8211733538506</v>
       </c>
       <c r="C10" t="n">
-        <v>528.9830385051386</v>
+        <v>242.8211733538506</v>
       </c>
       <c r="D10" t="n">
-        <v>528.9830385051386</v>
+        <v>286.79316170179</v>
       </c>
       <c r="E10" t="n">
-        <v>528.9830385051386</v>
+        <v>404.6220659132031</v>
       </c>
       <c r="F10" t="n">
         <v>528.9830385051386</v>
@@ -4983,22 +4983,22 @@
         <v>70.93025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>259.005934252978</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="U10" t="n">
-        <v>259.005934252978</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="V10" t="n">
-        <v>291.5717320076705</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="W10" t="n">
-        <v>291.5717320076705</v>
+        <v>242.8211733538506</v>
       </c>
       <c r="X10" t="n">
-        <v>291.5717320076705</v>
+        <v>242.8211733538506</v>
       </c>
       <c r="Y10" t="n">
-        <v>402.9810326867027</v>
+        <v>242.8211733538506</v>
       </c>
     </row>
     <row r="11">
@@ -5008,46 +5008,46 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C11" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D11" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E11" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F11" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G11" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H11" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I11" t="n">
         <v>44.72</v>
       </c>
       <c r="J11" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M11" t="n">
-        <v>555.568828728935</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N11" t="n">
-        <v>1108.978828728935</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O11" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P11" t="n">
         <v>1797.400904947332</v>
@@ -5071,13 +5071,13 @@
         <v>1265.70093914513</v>
       </c>
       <c r="W11" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X11" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y11" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="12">
@@ -5093,10 +5093,10 @@
         <v>461.5662247731743</v>
       </c>
       <c r="D12" t="n">
-        <v>373.7498342171993</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E12" t="n">
-        <v>373.7498342171993</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F12" t="n">
         <v>373.7498342171993</v>
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C13" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D13" t="n">
         <v>1010.366979583462</v>
@@ -5220,22 +5220,22 @@
         <v>44.72</v>
       </c>
       <c r="T13" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U13" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V13" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X13" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y13" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="14">
@@ -5245,49 +5245,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G14" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>1151.54</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M14" t="n">
-        <v>1662.388828728935</v>
+        <v>436.0291130376558</v>
       </c>
       <c r="N14" t="n">
-        <v>2215.798828728935</v>
+        <v>989.4391130376557</v>
       </c>
       <c r="O14" t="n">
-        <v>2215.798828728935</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="P14" t="n">
-        <v>2215.798828728935</v>
+        <v>2096.259113037655</v>
       </c>
       <c r="Q14" t="n">
         <v>2236</v>
@@ -5296,25 +5296,25 @@
         <v>2236</v>
       </c>
       <c r="S14" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>119.2429040110725</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C15" t="n">
-        <v>108.0308712378206</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D15" t="n">
-        <v>108.0308712378206</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E15" t="n">
-        <v>108.0308712378206</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F15" t="n">
         <v>44.72</v>
@@ -5375,25 +5375,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S15" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T15" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U15" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V15" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W15" t="n">
-        <v>274.6072361907174</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X15" t="n">
-        <v>204.0388125085078</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y15" t="n">
-        <v>154.1485167851397</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="16">
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C17" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D17" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E17" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F17" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G17" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H17" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
@@ -5509,13 +5509,13 @@
         <v>44.72</v>
       </c>
       <c r="K17" t="n">
-        <v>598.13</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="L17" t="n">
-        <v>598.13</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M17" t="n">
-        <v>1108.978828728935</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N17" t="n">
         <v>1243.990904947333</v>
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>398.9989442256527</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C18" t="n">
-        <v>387.7869114524009</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D18" t="n">
-        <v>387.7869114524009</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E18" t="n">
-        <v>387.7869114524009</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F18" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G18" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="H18" t="n">
-        <v>44.72</v>
+        <v>126.0429043828499</v>
       </c>
       <c r="I18" t="n">
         <v>44.72</v>
@@ -5606,31 +5606,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>1126.373107047762</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>927.106645136268</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S18" t="n">
-        <v>809.3652310305999</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T18" t="n">
-        <v>753.4482964674547</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U18" t="n">
-        <v>702.730761356155</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V18" t="n">
-        <v>637.5684712637103</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W18" t="n">
-        <v>554.3632764052976</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X18" t="n">
-        <v>483.794852723088</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y18" t="n">
-        <v>433.9045569997199</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="19">
@@ -5743,25 +5743,25 @@
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K20" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="L20" t="n">
-        <v>436.0291130376557</v>
+        <v>1151.54</v>
       </c>
       <c r="M20" t="n">
-        <v>946.8779417665908</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="N20" t="n">
-        <v>1500.287941766591</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="O20" t="n">
-        <v>2053.697941766591</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="P20" t="n">
-        <v>2053.697941766591</v>
+        <v>2236</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
@@ -5770,16 +5770,16 @@
         <v>2236</v>
       </c>
       <c r="S20" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T20" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U20" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V20" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W20" t="n">
         <v>970.4091539265823</v>
@@ -5858,13 +5858,13 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V21" t="n">
-        <v>648.0369133466629</v>
+        <v>648.036913346663</v>
       </c>
       <c r="W21" t="n">
-        <v>564.8317184882503</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X21" t="n">
-        <v>494.2632948060407</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y21" t="n">
         <v>90.8376455473191</v>
@@ -5937,16 +5937,16 @@
         <v>380.3468717970915</v>
       </c>
       <c r="V22" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W22" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X22" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y22" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="23">
@@ -5980,16 +5980,16 @@
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K23" t="n">
-        <v>690.5809049473327</v>
+        <v>44.72</v>
       </c>
       <c r="L23" t="n">
-        <v>690.5809049473327</v>
+        <v>44.72</v>
       </c>
       <c r="M23" t="n">
-        <v>690.5809049473327</v>
+        <v>555.568828728935</v>
       </c>
       <c r="N23" t="n">
         <v>690.5809049473327</v>
@@ -6004,10 +6004,10 @@
         <v>2236</v>
       </c>
       <c r="R23" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S23" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T23" t="n">
         <v>1846.617029377474</v>
@@ -6038,16 +6038,16 @@
         <v>472.7782575464261</v>
       </c>
       <c r="C24" t="n">
-        <v>108.0308712378207</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D24" t="n">
-        <v>108.0308712378207</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="E24" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="F24" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="G24" t="n">
         <v>44.72</v>
@@ -6132,13 +6132,13 @@
         <v>1265.174204945903</v>
       </c>
       <c r="H25" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I25" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J25" t="n">
-        <v>1868.407409693835</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K25" t="n">
         <v>1921.561060958496</v>
@@ -6220,7 +6220,7 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L26" t="n">
         <v>989.4391130376558</v>
@@ -6229,10 +6229,10 @@
         <v>989.4391130376558</v>
       </c>
       <c r="N26" t="n">
-        <v>1243.990904947333</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="O26" t="n">
-        <v>1797.400904947332</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="P26" t="n">
         <v>1797.400904947332</v>
@@ -6244,10 +6244,10 @@
         <v>2236</v>
       </c>
       <c r="S26" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T26" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U26" t="n">
         <v>1544.373295489988</v>
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>391.4553531635761</v>
+        <v>407.3842417608302</v>
       </c>
       <c r="C27" t="n">
-        <v>380.2433203903244</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D27" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="E27" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F27" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G27" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H27" t="n">
         <v>44.72</v>
@@ -6332,16 +6332,16 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V27" t="n">
-        <v>630.0248802016338</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W27" t="n">
-        <v>546.8196853432211</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X27" t="n">
-        <v>476.2512616610114</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y27" t="n">
-        <v>426.3609659376434</v>
+        <v>442.2898545348975</v>
       </c>
     </row>
     <row r="28">
@@ -6457,22 +6457,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L29" t="n">
-        <v>436.0291130376557</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="M29" t="n">
-        <v>946.8779417665908</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N29" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O29" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P29" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q29" t="n">
         <v>2236</v>
@@ -6487,13 +6487,13 @@
         <v>1850.622475221327</v>
       </c>
       <c r="U29" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V29" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W29" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X29" t="n">
         <v>725.6800292188371</v>
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C30" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D30" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E30" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="F30" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="G30" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="H30" t="n">
         <v>44.72</v>
@@ -6560,25 +6560,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S30" t="n">
-        <v>819.8336731135525</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T30" t="n">
-        <v>763.9167385504073</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U30" t="n">
-        <v>713.1992034391076</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V30" t="n">
-        <v>648.0369133466629</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W30" t="n">
-        <v>564.8317184882503</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X30" t="n">
-        <v>494.2632948060407</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y30" t="n">
-        <v>444.3729990826727</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="31">
@@ -6679,13 +6679,13 @@
         <v>217.0655061454243</v>
       </c>
       <c r="F32" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G32" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H32" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I32" t="n">
         <v>44.72</v>
@@ -6694,22 +6694,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>618.3311712710653</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L32" t="n">
-        <v>618.3311712710653</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M32" t="n">
-        <v>1129.18</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N32" t="n">
-        <v>1129.18</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O32" t="n">
-        <v>1682.59</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="P32" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q32" t="n">
         <v>2236</v>
@@ -6803,16 +6803,16 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U33" t="n">
-        <v>713.1992034391076</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V33" t="n">
-        <v>648.0369133466629</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W33" t="n">
-        <v>564.8317184882503</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X33" t="n">
-        <v>494.2632948060407</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y33" t="n">
         <v>90.8376455473191</v>
@@ -6919,10 +6919,10 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G35" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H35" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I35" t="n">
         <v>44.72</v>
@@ -6934,13 +6934,13 @@
         <v>436.0291130376557</v>
       </c>
       <c r="L35" t="n">
-        <v>436.0291130376557</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M35" t="n">
-        <v>946.8779417665908</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N35" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O35" t="n">
         <v>1797.400904947332</v>
@@ -6986,16 +6986,16 @@
         <v>472.7782575464261</v>
       </c>
       <c r="C36" t="n">
-        <v>390.8534315372855</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D36" t="n">
-        <v>390.8534315372855</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E36" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F36" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G36" t="n">
         <v>44.72</v>
@@ -7062,31 +7062,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C37" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D37" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E37" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F37" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G37" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H37" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I37" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J37" t="n">
-        <v>1868.407409693835</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K37" t="n">
         <v>1921.561060958496</v>
@@ -7150,16 +7150,16 @@
         <v>271.977919889736</v>
       </c>
       <c r="E38" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F38" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G38" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
@@ -7177,13 +7177,13 @@
         <v>1662.388828728935</v>
       </c>
       <c r="N38" t="n">
-        <v>2215.798828728935</v>
+        <v>1682.59</v>
       </c>
       <c r="O38" t="n">
-        <v>2215.798828728935</v>
+        <v>1682.59</v>
       </c>
       <c r="P38" t="n">
-        <v>2215.798828728935</v>
+        <v>2236</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
@@ -7220,19 +7220,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D39" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="E39" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="F39" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="G39" t="n">
         <v>44.72</v>
@@ -7268,28 +7268,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V39" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y39" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="40">
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C40" t="n">
         <v>946.5478354584615</v>
@@ -7362,13 +7362,13 @@
         <v>529.6682646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7378,43 +7378,43 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C41" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D41" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E41" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F41" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G41" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H41" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K41" t="n">
-        <v>989.4391130376558</v>
+        <v>598.13</v>
       </c>
       <c r="L41" t="n">
-        <v>1243.990904947333</v>
+        <v>1151.54</v>
       </c>
       <c r="M41" t="n">
-        <v>1243.990904947333</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="N41" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O41" t="n">
         <v>1797.400904947332</v>
@@ -7426,28 +7426,28 @@
         <v>2236</v>
       </c>
       <c r="R41" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S41" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U41" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V41" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W41" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X41" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y41" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="42">
@@ -7457,10 +7457,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>407.3842417608302</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D42" t="n">
         <v>44.72</v>
@@ -7502,31 +7502,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q42" t="n">
-        <v>1136.841549130715</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>937.5750872192207</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>466.2983195781991</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T42" t="n">
-        <v>410.3813850150538</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U42" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V42" t="n">
-        <v>294.5015598113094</v>
+        <v>645.9537687988877</v>
       </c>
       <c r="W42" t="n">
-        <v>211.2963649528968</v>
+        <v>562.7485739404751</v>
       </c>
       <c r="X42" t="n">
-        <v>140.7279412706871</v>
+        <v>492.1801502582655</v>
       </c>
       <c r="Y42" t="n">
-        <v>90.8376455473191</v>
+        <v>442.2898545348975</v>
       </c>
     </row>
     <row r="43">
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C43" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D43" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E43" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F43" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G43" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H43" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I43" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J43" t="n">
         <v>1860.696627021627</v>
@@ -7590,22 +7590,22 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U43" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X43" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y43" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="44">
@@ -7627,13 +7627,13 @@
         <v>217.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G44" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
@@ -7642,22 +7642,22 @@
         <v>44.72</v>
       </c>
       <c r="K44" t="n">
-        <v>44.72</v>
+        <v>598.13</v>
       </c>
       <c r="L44" t="n">
-        <v>598.13</v>
+        <v>1151.54</v>
       </c>
       <c r="M44" t="n">
-        <v>1108.978828728935</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="N44" t="n">
-        <v>1662.388828728935</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="O44" t="n">
-        <v>1797.400904947332</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="P44" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7745,25 +7745,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T45" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U45" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V45" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W45" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X45" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y45" t="n">
-        <v>90.8376455473191</v>
+        <v>444.3729990826727</v>
       </c>
     </row>
     <row r="46">
@@ -7827,19 +7827,19 @@
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U46" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V46" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W46" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X46" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y46" t="n">
         <v>807.7884919737335</v>
@@ -7964,10 +7964,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>403.9898989898991</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -7979,7 +7979,7 @@
         <v>898.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>78.97603822292498</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P2" t="n">
         <v>421.2870600406814</v>
@@ -8201,22 +8201,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
         <v>421</v>
       </c>
       <c r="L5" t="n">
-        <v>421.0000000000001</v>
+        <v>421</v>
       </c>
       <c r="M5" t="n">
-        <v>948.2520266322163</v>
+        <v>965.2621276423173</v>
       </c>
       <c r="N5" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>491.2478695740924</v>
+        <v>78.97603822292498</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
@@ -8438,25 +8438,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="M8" t="n">
-        <v>965.2621276423173</v>
+        <v>552.9902962911499</v>
       </c>
       <c r="N8" t="n">
         <v>898.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>474.2377685639915</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P8" t="n">
-        <v>421.2870600406814</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
         <v>172.8226843274854</v>
@@ -8675,7 +8675,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8690,10 +8690,10 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>206.6237041381304</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P11" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8912,28 +8912,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N14" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q14" t="n">
-        <v>193.2279078336117</v>
+        <v>313.9750954005607</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,7 +9152,7 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9161,7 +9161,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>613.6247926338732</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
         <v>629.2478695740924</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
         <v>629.2478695740924</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>20.69228354680773</v>
       </c>
       <c r="Q20" t="n">
-        <v>356.9661774925453</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K23" t="n">
-        <v>257.1230221309868</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>477.2489580698352</v>
+        <v>613.6247926338732</v>
       </c>
       <c r="O23" t="n">
         <v>629.2478695740924</v>
@@ -9863,22 +9863,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>559</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>544.2621276423173</v>
       </c>
       <c r="N26" t="n">
-        <v>734.3719802008219</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O26" t="n">
         <v>629.2478695740924</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>257.410082171668</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10100,25 +10100,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>257.1230221309868</v>
       </c>
       <c r="M29" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N29" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
-        <v>184.4305532057413</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,7 +10337,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>184.1434931650601</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10346,16 +10346,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
-        <v>559.2870600406815</v>
+        <v>300.4011642636528</v>
       </c>
       <c r="Q32" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10577,7 +10577,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
@@ -10586,7 +10586,7 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
-        <v>370.3619737970638</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
         <v>0.2870600406814136</v>
@@ -10820,16 +10820,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>1036.248958069835</v>
+        <v>497.6541815759616</v>
       </c>
       <c r="O38" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q38" t="n">
-        <v>193.2279078336117</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,22 +11045,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
         <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>257.1230221309868</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>477.2489580698352</v>
+        <v>613.624792633873</v>
       </c>
       <c r="O41" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
@@ -11285,10 +11285,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
@@ -11297,13 +11297,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>206.6237041381302</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2870600406814136</v>
+        <v>20.69228354680773</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -26281,10 +26281,10 @@
         <v>1448283.596382484</v>
       </c>
       <c r="F2" t="n">
-        <v>1448283.596382484</v>
+        <v>1448283.596382485</v>
       </c>
       <c r="G2" t="n">
-        <v>1448283.596382484</v>
+        <v>1448283.596382485</v>
       </c>
       <c r="H2" t="n">
         <v>1448283.596382484</v>
@@ -26293,13 +26293,13 @@
         <v>1448283.596382484</v>
       </c>
       <c r="J2" t="n">
-        <v>1448283.596382484</v>
+        <v>1448283.596382485</v>
       </c>
       <c r="K2" t="n">
         <v>1448283.596382484</v>
       </c>
       <c r="L2" t="n">
-        <v>1448283.596382485</v>
+        <v>1448283.596382483</v>
       </c>
       <c r="M2" t="n">
         <v>1448283.596382484</v>
@@ -26308,10 +26308,10 @@
         <v>1448283.596382484</v>
       </c>
       <c r="O2" t="n">
-        <v>1448283.596382485</v>
+        <v>1448283.596382484</v>
       </c>
       <c r="P2" t="n">
-        <v>1448283.596382484</v>
+        <v>1448283.596382483</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566354.9592425094</v>
+        <v>567917.5723359546</v>
       </c>
       <c r="C4" t="n">
-        <v>564322.4434789647</v>
+        <v>565885.0565724098</v>
       </c>
       <c r="D4" t="n">
-        <v>562287.1704809261</v>
+        <v>563849.7835743712</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128454</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533137.9258114471</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380802</v>
+        <v>531178.6502511877</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116067</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>674512.2371399748</v>
+        <v>672949.6240465292</v>
       </c>
       <c r="C6" t="n">
-        <v>824736.7529035195</v>
+        <v>823174.139810074</v>
       </c>
       <c r="D6" t="n">
-        <v>826772.0259015582</v>
+        <v>825209.4128081126</v>
       </c>
       <c r="E6" t="n">
-        <v>513202.1931559489</v>
+        <v>511460.3433428413</v>
       </c>
       <c r="F6" t="n">
-        <v>843721.0885014533</v>
+        <v>841979.2386883459</v>
       </c>
       <c r="G6" t="n">
-        <v>845666.6649696387</v>
+        <v>843924.8151565314</v>
       </c>
       <c r="H6" t="n">
-        <v>847614.9417869401</v>
+        <v>845873.091973832</v>
       </c>
       <c r="I6" t="n">
-        <v>849565.9384303001</v>
+        <v>847824.0886171927</v>
       </c>
       <c r="J6" t="n">
-        <v>423327.674631925</v>
+        <v>421585.824818818</v>
       </c>
       <c r="K6" t="n">
-        <v>853476.1703841446</v>
+        <v>851734.320571037</v>
       </c>
       <c r="L6" t="n">
-        <v>855435.4459444043</v>
+        <v>853693.5961312954</v>
       </c>
       <c r="M6" t="n">
-        <v>808821.5218403836</v>
+        <v>807079.6720272755</v>
       </c>
       <c r="N6" t="n">
-        <v>859362.4188752364</v>
+        <v>857620.5690621289</v>
       </c>
       <c r="O6" t="n">
-        <v>581330.1581329756</v>
+        <v>579588.3083198668</v>
       </c>
       <c r="P6" t="n">
-        <v>863300.7609839847</v>
+        <v>861558.9111708767</v>
       </c>
     </row>
   </sheetData>
@@ -26984,7 +26984,7 @@
         <v>350</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -26999,7 +26999,7 @@
         <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
@@ -27008,7 +27008,7 @@
         <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>350</v>
@@ -27027,7 +27027,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -27036,16 +27036,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>-0</v>
@@ -27097,13 +27097,13 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>421</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -27436,7 +27436,7 @@
         <v>400</v>
       </c>
       <c r="C2" t="n">
-        <v>400</v>
+        <v>231.5850086145855</v>
       </c>
       <c r="D2" t="n">
         <v>400</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>82.46360744287983</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27521,7 +27521,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
@@ -27530,7 +27530,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>90.84076273253172</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -27557,10 +27557,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>126.2737972923793</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>99.3015901195177</v>
       </c>
     </row>
     <row r="4">
@@ -27591,25 +27591,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>357.4276244676886</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
         <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
@@ -27618,7 +27618,7 @@
         <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,10 +27642,10 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
         <v>150.9583912744579</v>
@@ -27657,10 +27657,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>394.129344461397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27685,7 +27685,7 @@
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>231.5850086145855</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
         <v>400</v>
@@ -27727,7 +27727,7 @@
         <v>400</v>
       </c>
       <c r="U5" t="n">
-        <v>400</v>
+        <v>231.5850086145855</v>
       </c>
       <c r="V5" t="n">
         <v>400</v>
@@ -27752,13 +27752,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>102.0728587298384</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27770,7 +27770,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>109.1275310436166</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27806,13 +27806,13 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>11.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27831,31 +27831,31 @@
         <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
         <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I7" t="n">
-        <v>228.542154274992</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>326.7382315552963</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27882,7 +27882,7 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
@@ -27961,7 +27961,7 @@
         <v>400</v>
       </c>
       <c r="T8" t="n">
-        <v>400</v>
+        <v>231.5850086145854</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -27970,7 +27970,7 @@
         <v>400</v>
       </c>
       <c r="W8" t="n">
-        <v>231.5850086145854</v>
+        <v>400</v>
       </c>
       <c r="X8" t="n">
         <v>400</v>
@@ -27992,13 +27992,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>220.0539558339848</v>
       </c>
       <c r="G9" t="n">
         <v>325.7395358750273</v>
@@ -28007,7 +28007,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,19 +28031,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>281.9106179544542</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
@@ -28068,16 +28068,16 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D10" t="n">
+        <v>329.952367901959</v>
+      </c>
+      <c r="E10" t="n">
         <v>400</v>
       </c>
-      <c r="D10" t="n">
-        <v>285.5362180555555</v>
-      </c>
-      <c r="E10" t="n">
-        <v>280.9809048369565</v>
-      </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
@@ -28119,22 +28119,22 @@
         <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
         <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
-        <v>232.0650554229763</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28207,7 +28207,7 @@
         <v>350</v>
       </c>
       <c r="W11" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="X11" t="n">
         <v>350</v>
@@ -28229,13 +28229,13 @@
         <v>350</v>
       </c>
       <c r="D12" t="n">
-        <v>260.9994602472874</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>252.6980156874616</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -28308,7 +28308,7 @@
         <v>350</v>
       </c>
       <c r="D13" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="E13" t="n">
         <v>350</v>
@@ -28356,7 +28356,7 @@
         <v>350</v>
       </c>
       <c r="T13" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U13" t="n">
         <v>350</v>
@@ -28402,7 +28402,7 @@
         <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28432,7 +28432,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T14" t="n">
         <v>350</v>
@@ -28469,10 +28469,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>269.6305770343469</v>
       </c>
       <c r="F15" t="n">
-        <v>276.9584798124345</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>325.7395358750273</v>
@@ -28511,7 +28511,7 @@
         <v>350</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T15" t="n">
         <v>350</v>
@@ -28618,7 +28618,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="C17" t="n">
         <v>350</v>
@@ -28639,7 +28639,7 @@
         <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28709,16 +28709,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H18" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>136.6167105523271</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>100.037744902914</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>350</v>
@@ -28906,7 +28906,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T20" t="n">
         <v>350</v>
@@ -28918,7 +28918,7 @@
         <v>350</v>
       </c>
       <c r="W20" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="X20" t="n">
         <v>350</v>
@@ -28994,16 +28994,16 @@
         <v>350</v>
       </c>
       <c r="V21" t="n">
-        <v>287.3222374745574</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="W21" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>350</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22">
@@ -29013,7 +29013,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="C22" t="n">
         <v>350</v>
@@ -29073,7 +29073,7 @@
         <v>350</v>
       </c>
       <c r="V22" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W22" t="n">
         <v>350</v>
@@ -29140,13 +29140,13 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S23" t="n">
         <v>350</v>
       </c>
       <c r="T23" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="U23" t="n">
         <v>350</v>
@@ -29174,19 +29174,19 @@
         <v>350</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>277.9320215941727</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>263.0617733495848</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H24" t="n">
         <v>332.1680871864211</v>
@@ -29268,7 +29268,7 @@
         <v>350</v>
       </c>
       <c r="H25" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="I25" t="n">
         <v>350</v>
@@ -29277,7 +29277,7 @@
         <v>350</v>
       </c>
       <c r="K25" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="L25" t="n">
         <v>350</v>
@@ -29380,13 +29380,13 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T26" t="n">
         <v>350</v>
       </c>
       <c r="U26" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="V26" t="n">
         <v>350</v>
@@ -29414,7 +29414,7 @@
         <v>350</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>342.6720972219126</v>
@@ -29426,7 +29426,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I27" t="n">
         <v>217.1263858913485</v>
@@ -29468,7 +29468,7 @@
         <v>350</v>
       </c>
       <c r="V27" t="n">
-        <v>269.4903246609786</v>
+        <v>350</v>
       </c>
       <c r="W27" t="n">
         <v>350</v>
@@ -29477,7 +29477,7 @@
         <v>350</v>
       </c>
       <c r="Y27" t="n">
-        <v>350</v>
+        <v>285.2599243722601</v>
       </c>
     </row>
     <row r="28">
@@ -29623,7 +29623,7 @@
         <v>350</v>
       </c>
       <c r="U29" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="V29" t="n">
         <v>350</v>
@@ -29632,7 +29632,7 @@
         <v>350</v>
       </c>
       <c r="X29" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="Y29" t="n">
         <v>350</v>
@@ -29645,7 +29645,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C30" t="n">
         <v>350</v>
@@ -29663,7 +29663,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H30" t="n">
-        <v>332.1680871864211</v>
+        <v>269.4903246609787</v>
       </c>
       <c r="I30" t="n">
         <v>217.1263858913485</v>
@@ -29696,7 +29696,7 @@
         <v>350</v>
       </c>
       <c r="S30" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="T30" t="n">
         <v>350</v>
@@ -29708,7 +29708,7 @@
         <v>350</v>
       </c>
       <c r="W30" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>350</v>
@@ -29815,7 +29815,7 @@
         <v>350</v>
       </c>
       <c r="F32" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="G32" t="n">
         <v>350</v>
@@ -29824,7 +29824,7 @@
         <v>350</v>
       </c>
       <c r="I32" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29939,19 +29939,19 @@
         <v>350</v>
       </c>
       <c r="U33" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="V33" t="n">
         <v>350</v>
       </c>
       <c r="W33" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>350</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>287.3222374745576</v>
       </c>
     </row>
     <row r="34">
@@ -30055,13 +30055,13 @@
         <v>350</v>
       </c>
       <c r="G35" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H35" t="n">
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30122,19 +30122,19 @@
         <v>350</v>
       </c>
       <c r="C36" t="n">
-        <v>279.99433469647</v>
+        <v>350</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>252.6980156874616</v>
       </c>
       <c r="G36" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>332.1680871864211</v>
@@ -30198,7 +30198,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="C37" t="n">
         <v>350</v>
@@ -30225,7 +30225,7 @@
         <v>350</v>
       </c>
       <c r="K37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="L37" t="n">
         <v>350</v>
@@ -30286,7 +30286,7 @@
         <v>350</v>
       </c>
       <c r="E38" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="F38" t="n">
         <v>350</v>
@@ -30298,7 +30298,7 @@
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30362,7 +30362,7 @@
         <v>350</v>
       </c>
       <c r="D39" t="n">
-        <v>260.9994602472874</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
@@ -30371,7 +30371,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
         <v>332.1680871864211</v>
@@ -30404,7 +30404,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>350</v>
@@ -30416,7 +30416,7 @@
         <v>350</v>
       </c>
       <c r="V39" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="W39" t="n">
         <v>350</v>
@@ -30438,7 +30438,7 @@
         <v>350</v>
       </c>
       <c r="C40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="D40" t="n">
         <v>350</v>
@@ -30498,7 +30498,7 @@
         <v>350</v>
       </c>
       <c r="W40" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="X40" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S41" t="n">
         <v>350</v>
@@ -30599,7 +30599,7 @@
         <v>350</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>342.6720972219126</v>
@@ -30638,13 +30638,13 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>110.4015025650371</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
         <v>350</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T42" t="n">
         <v>350</v>
@@ -30653,7 +30653,7 @@
         <v>350</v>
       </c>
       <c r="V42" t="n">
-        <v>350</v>
+        <v>285.25992437226</v>
       </c>
       <c r="W42" t="n">
         <v>350</v>
@@ -30696,7 +30696,7 @@
         <v>350</v>
       </c>
       <c r="J43" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K43" t="n">
         <v>350</v>
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30763,7 +30763,7 @@
         <v>350</v>
       </c>
       <c r="F44" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="G44" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>350</v>
@@ -30881,7 +30881,7 @@
         <v>350</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T45" t="n">
         <v>350</v>
@@ -30893,13 +30893,13 @@
         <v>350</v>
       </c>
       <c r="W45" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="X45" t="n">
         <v>350</v>
       </c>
       <c r="Y45" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
     </row>
     <row r="46">
@@ -30963,7 +30963,7 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -30978,7 +30978,7 @@
         <v>350</v>
       </c>
       <c r="Y46" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -34743,10 +34743,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>403.9898989898991</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -34758,7 +34758,7 @@
         <v>421</v>
       </c>
       <c r="O2" t="n">
-        <v>8.728168648832536</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>421</v>
@@ -34877,25 +34877,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>84.70237781964397</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
         <v>223.3665443798817</v>
@@ -34904,7 +34904,7 @@
         <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,10 +34928,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -34943,10 +34943,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>106.6639916119346</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34980,22 +34980,22 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K5" t="n">
         <v>421</v>
       </c>
       <c r="L5" t="n">
-        <v>421.0000000000001</v>
+        <v>421</v>
       </c>
       <c r="M5" t="n">
-        <v>403.9898989898989</v>
+        <v>421</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>421</v>
+        <v>8.728168648832536</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -35117,31 +35117,31 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>51.9086986548737</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>38.21745775415324</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35168,7 +35168,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>249.0416087255421</v>
@@ -35217,25 +35217,25 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="M8" t="n">
-        <v>421</v>
+        <v>8.728168648832536</v>
       </c>
       <c r="N8" t="n">
         <v>421</v>
       </c>
       <c r="O8" t="n">
-        <v>403.989898989899</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35354,16 +35354,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>44.41614984640352</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
         <v>154.95612715847</v>
@@ -35405,22 +35405,22 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>32.89474520676014</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,7 +35454,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -35469,10 +35469,10 @@
         <v>559</v>
       </c>
       <c r="O11" t="n">
-        <v>136.375834564038</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35594,7 +35594,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D13" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857869</v>
       </c>
       <c r="E13" t="n">
         <v>69.01909516304346</v>
@@ -35642,7 +35642,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U13" t="n">
         <v>199.0416087255421</v>
@@ -35691,28 +35691,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.40522350612631</v>
+        <v>141.1524110730753</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35931,7 +35931,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -35940,7 +35940,7 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>136.375834564038</v>
+        <v>559</v>
       </c>
       <c r="O17" t="n">
         <v>559</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>559</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>20.40522350612631</v>
       </c>
       <c r="Q20" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36299,7 +36299,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>62.88619966292134</v>
+        <v>55.09753029705556</v>
       </c>
       <c r="C22" t="n">
         <v>77.27475335195533</v>
@@ -36359,7 +36359,7 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V22" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W22" t="n">
         <v>123.6271901612903</v>
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>257.1230221309868</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="O23" t="n">
         <v>559</v>
@@ -36554,7 +36554,7 @@
         <v>104.95612715847</v>
       </c>
       <c r="H25" t="n">
-        <v>121.2288738983814</v>
+        <v>113.4402045325156</v>
       </c>
       <c r="I25" t="n">
         <v>173.3665443798817</v>
@@ -36563,7 +36563,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K25" t="n">
-        <v>53.69055683299113</v>
+        <v>61.47922619885696</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36642,22 +36642,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>559</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>257.1230221309867</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>559</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36879,25 +36879,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>257.1230221309868</v>
       </c>
       <c r="M29" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37116,7 +37116,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>184.1434931650601</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -37125,16 +37125,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37356,7 +37356,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="M35" t="n">
         <v>516.0089179080152</v>
@@ -37365,7 +37365,7 @@
         <v>559</v>
       </c>
       <c r="O35" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -37484,7 +37484,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>62.88619966292134</v>
+        <v>55.09753029705556</v>
       </c>
       <c r="C37" t="n">
         <v>77.27475335195533</v>
@@ -37511,7 +37511,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K37" t="n">
-        <v>53.69055683299113</v>
+        <v>61.47922619885696</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -37599,16 +37599,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
+        <v>20.40522350612631</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
         <v>559</v>
       </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
       <c r="Q38" t="n">
-        <v>20.40522350612631</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37724,7 +37724,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C40" t="n">
-        <v>69.48608398608951</v>
+        <v>77.27475335195533</v>
       </c>
       <c r="D40" t="n">
         <v>64.46378194444452</v>
@@ -37784,7 +37784,7 @@
         <v>150.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>123.6271901612903</v>
+        <v>115.8385207954244</v>
       </c>
       <c r="X40" t="n">
         <v>102.5563545698924</v>
@@ -37824,22 +37824,22 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>257.1230221309868</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="O41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -37982,7 +37982,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J43" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K43" t="n">
         <v>61.47922619885696</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38064,10 +38064,10 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
@@ -38076,13 +38076,13 @@
         <v>559</v>
       </c>
       <c r="O44" t="n">
-        <v>136.3758345640378</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>20.40522350612631</v>
       </c>
       <c r="Q44" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
@@ -38264,7 +38264,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y46" t="n">
-        <v>54.74597778467183</v>
+        <v>62.53464715053764</v>
       </c>
     </row>
   </sheetData>
